--- a/Config/Excel/LevelConfig.xlsx
+++ b/Config/Excel/LevelConfig.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
   <si>
     <t>Id</t>
   </si>
@@ -58,6 +58,9 @@
     <t>NeedStraightNum</t>
   </si>
   <si>
+    <t>LevelEvent</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -83,6 +86,9 @@
   </si>
   <si>
     <t>需要接龙数</t>
+  </si>
+  <si>
+    <t>关卡开始事件</t>
   </si>
   <si>
     <t>01010101</t>
@@ -1070,20 +1076,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.8888888888889" customWidth="1"/>
-    <col min="2" max="2" width="24.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="9.26851851851852" customWidth="1"/>
     <col min="3" max="3" width="22.3148148148148" customWidth="1"/>
     <col min="4" max="4" width="19.8055555555556" customWidth="1"/>
     <col min="5" max="5" width="19.6018518518519" customWidth="1"/>
     <col min="6" max="6" width="22.8888888888889" customWidth="1"/>
     <col min="7" max="7" width="19.8981481481481" style="1" customWidth="1"/>
     <col min="8" max="8" width="18.5462962962963" customWidth="1"/>
+    <col min="9" max="9" width="18.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1106,58 +1113,67 @@
       <c r="H1" t="s">
         <v>6</v>
       </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="H2" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="I2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="3">
@@ -1173,15 +1189,18 @@
         <v>4</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H4">
         <v>2</v>
       </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1190,12 +1209,12 @@
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1210,15 +1229,18 @@
         <v>3</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H6">
         <v>3</v>
       </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1233,15 +1255,18 @@
         <v>3</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H7">
         <v>3</v>
       </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1250,12 +1275,12 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1264,12 +1289,12 @@
         <v>0</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1284,15 +1309,18 @@
         <v>2</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H10">
         <v>3</v>
       </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1307,15 +1335,18 @@
         <v>3</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H11">
         <v>3</v>
       </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1330,15 +1361,18 @@
         <v>2</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H12">
         <v>3</v>
       </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1347,12 +1381,12 @@
         <v>0</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -1368,6 +1402,9 @@
       </c>
       <c r="H14">
         <v>4</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
